--- a/Result/profitability/8272.xlsx
+++ b/Result/profitability/8272.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM18"/>
+  <dimension ref="A1:AM19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-1.55</v>
       </c>
       <c r="M2" t="n">
-        <v>0.81375</v>
+        <v>0.85375</v>
       </c>
       <c r="N2" t="n">
-        <v>75.76000000000001</v>
+        <v>75.90625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.76</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8162499999999999</v>
+        <v>0.665</v>
       </c>
       <c r="N3" t="n">
-        <v>78.25375</v>
+        <v>77.38249999999999</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -2716,6 +2716,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>8272</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>120</v>
+      </c>
+      <c r="D19" t="n">
+        <v>31</v>
+      </c>
+      <c r="E19" t="n">
+        <v>89</v>
+      </c>
+      <c r="F19" t="n">
+        <v>73.88</v>
+      </c>
+      <c r="G19" t="n">
+        <v>24</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>20.00%</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>27</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N19" t="n">
+        <v>74.74250000000001</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.717948717948718</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-1.100000000000009</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-0.01467057882101908</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-0.1653543307086613</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-4.450000000000003</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-0.05681092812460109</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK19" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
